--- a/References/Hybrid SDLC Agile Templates/GSI - NONOS - DAVID - Hybrid SDLC Agile.xlsx
+++ b/References/Hybrid SDLC Agile Templates/GSI - NONOS - DAVID - Hybrid SDLC Agile.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="245">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="247">
   <si>
     <t>Template Name</t>
   </si>
@@ -609,6 +609,12 @@
   </si>
   <si>
     <t>Use the matrix as the cross-department reporting view. Milestone marks the primary owning department and Waiting is the recommended initial state; replace these with current status or target week as planning progresses. Imported Sub-Tasks remain the source of progress percentages.</t>
+  </si>
+  <si>
+    <t>Parallel planning</t>
+  </si>
+  <si>
+    <t>Independent departmental readiness checkpoints run in parallel after the target workflow is approved. LINK HUB business processes also run as parallel workstreams; design/build/QA/UAT/release gates inside each process remain sequential.</t>
   </si>
   <si>
     <t>Task Board</t>
@@ -7794,8 +7800,12 @@
       </c>
     </row>
     <row r="14" spans="1:2">
-      <c r="A14" s="2"/>
-      <c r="B14" s="2"/>
+      <c r="A14" s="2" t="s">
+        <v>208</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>209</v>
+      </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="2"/>
@@ -8564,7 +8574,7 @@
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" s="4" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="B1" s="4"/>
       <c r="C1" s="4"/>
@@ -8572,30 +8582,30 @@
     </row>
     <row r="2" spans="1:4">
       <c r="A2" s="2" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
     </row>
     <row r="3" spans="1:4">
       <c r="A3" s="2" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -8603,13 +8613,13 @@
         <v>10</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -8617,41 +8627,41 @@
         <v>8</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
     </row>
     <row r="6" spans="1:4">
       <c r="A6" s="2" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
     </row>
     <row r="7" spans="1:4">
       <c r="A7" s="2" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -9832,22 +9842,22 @@
   <sheetData>
     <row r="1" spans="1:6">
       <c r="A1" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="B1" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="C1" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="D1" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="E1" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="F1" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
     </row>
     <row r="2" spans="1:6">
@@ -9855,13 +9865,13 @@
         <v>27</v>
       </c>
       <c r="B2" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="C2" t="s">
         <v>29</v>
       </c>
       <c r="D2" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="E2" t="s">
         <v>34</v>
@@ -9872,30 +9882,30 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="B3" t="s">
         <v>28</v>
       </c>
       <c r="C3" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="D3" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="E3" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="F3" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
     </row>
     <row r="4" spans="1:6">
       <c r="B4" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="C4" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="D4" t="s">
         <v>31</v>
@@ -9903,7 +9913,7 @@
     </row>
     <row r="5" spans="1:6">
       <c r="B5" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
     </row>
   </sheetData>
